--- a/docs/Suivi_Projet_Rational_Final.xlsx
+++ b/docs/Suivi_Projet_Rational_Final.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Etude\Projet\Evaluation\prestashop_ui\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA5DD23C-803C-4337-BDAF-5E434C1E7C8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37ABFB3B-ABB1-4636-8473-981064E58492}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Recap" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="143">
   <si>
     <t>Qui</t>
   </si>
@@ -408,7 +408,61 @@
     <t>Validation finale du workflow client complet</t>
   </si>
   <si>
-    <t>TOTAL</t>
+    <t>existingapp</t>
+  </si>
+  <si>
+    <t>Creation api pour gerer statut livre et annule dans l'existing app</t>
+  </si>
+  <si>
+    <t>metier</t>
+  </si>
+  <si>
+    <t>shared</t>
+  </si>
+  <si>
+    <t>Api</t>
+  </si>
+  <si>
+    <t>Utilisation de l'api cree dans mon new app</t>
+  </si>
+  <si>
+    <t>integration</t>
+  </si>
+  <si>
+    <t>State</t>
+  </si>
+  <si>
+    <t>Mise a jour du liste de commande pour inclure seulement le choix de annule et livre</t>
+  </si>
+  <si>
+    <t>affichage</t>
+  </si>
+  <si>
+    <t>Statistique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Creation du page de statistique pour afficher total vente HT, total achat HC, </t>
+  </si>
+  <si>
+    <t>Logique</t>
+  </si>
+  <si>
+    <t>Calcule des statisatique</t>
+  </si>
+  <si>
+    <t>Metier</t>
+  </si>
+  <si>
+    <t>calcule marge</t>
+  </si>
+  <si>
+    <t>Affichage du tableau pour affiche qte physique, reserver, dispo</t>
+  </si>
+  <si>
+    <t>Recuperation des donne a affiche</t>
+  </si>
+  <si>
+    <t>Integration de la logique a l'affichage</t>
   </si>
 </sst>
 </file>
@@ -814,11 +868,11 @@
       </c>
       <c r="B2">
         <f>'Detail Avancement'!H53</f>
-        <v>5290</v>
+        <v>60</v>
       </c>
       <c r="C2">
         <f>'Detail Avancement'!I53</f>
-        <v>5290</v>
+        <v>60</v>
       </c>
       <c r="D2">
         <f>'Detail Avancement'!J53</f>
@@ -831,11 +885,11 @@
       </c>
       <c r="B3" s="2">
         <f>B2</f>
-        <v>5290</v>
+        <v>60</v>
       </c>
       <c r="C3" s="2">
         <f>C2</f>
-        <v>5290</v>
+        <v>60</v>
       </c>
       <c r="D3" s="2">
         <f>D2</f>
@@ -888,11 +942,11 @@
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
         <f>Recap!B3</f>
-        <v>5290</v>
+        <v>60</v>
       </c>
       <c r="B2">
         <f>Recap!C3</f>
-        <v>5290</v>
+        <v>60</v>
       </c>
       <c r="C2">
         <f>Recap!D3</f>
@@ -2326,14 +2380,14 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:K53"/>
+  <dimension ref="A1:K62"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.21875" customWidth="1"/>
     <col min="2" max="2" width="16.21875" customWidth="1"/>
     <col min="3" max="3" width="11.33203125" customWidth="1"/>
     <col min="4" max="4" width="13.88671875" customWidth="1"/>
-    <col min="5" max="5" width="59.33203125" customWidth="1"/>
+    <col min="5" max="5" width="69.109375" customWidth="1"/>
     <col min="6" max="6" width="18" customWidth="1"/>
     <col min="7" max="7" width="9.77734375" customWidth="1"/>
     <col min="8" max="8" width="17.33203125" customWidth="1"/>
@@ -2412,7 +2466,7 @@
         <v>0</v>
       </c>
       <c r="K2" s="6">
-        <f t="shared" ref="K2:K32" si="1">IF(H2&gt;0, I2/H2, 0)</f>
+        <f>IF(H2&gt;0, I2/H2, 0)</f>
         <v>1</v>
       </c>
     </row>
@@ -2442,7 +2496,7 @@
         <v>20</v>
       </c>
       <c r="I3">
-        <f t="shared" ref="I3:I52" si="2">H3</f>
+        <f t="shared" ref="I3:I53" si="1">H3</f>
         <v>20</v>
       </c>
       <c r="J3">
@@ -2450,7 +2504,7 @@
         <v>0</v>
       </c>
       <c r="K3" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="K3:K32" si="2">IF(H3&gt;0, I3/H3, 0)</f>
         <v>1</v>
       </c>
     </row>
@@ -2481,7 +2535,7 @@
         <v>40</v>
       </c>
       <c r="I4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>40</v>
       </c>
       <c r="J4">
@@ -2489,7 +2543,7 @@
         <v>0</v>
       </c>
       <c r="K4" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -2520,7 +2574,7 @@
         <v>20</v>
       </c>
       <c r="I5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="J5">
@@ -2528,7 +2582,7 @@
         <v>0</v>
       </c>
       <c r="K5" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -2559,7 +2613,7 @@
         <v>15</v>
       </c>
       <c r="I6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
       <c r="J6">
@@ -2567,7 +2621,7 @@
         <v>0</v>
       </c>
       <c r="K6" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -2598,7 +2652,7 @@
         <v>25</v>
       </c>
       <c r="I7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>25</v>
       </c>
       <c r="J7">
@@ -2606,7 +2660,7 @@
         <v>0</v>
       </c>
       <c r="K7" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -2637,7 +2691,7 @@
         <v>30</v>
       </c>
       <c r="I8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>30</v>
       </c>
       <c r="J8">
@@ -2645,7 +2699,7 @@
         <v>0</v>
       </c>
       <c r="K8" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -2676,7 +2730,7 @@
         <v>30</v>
       </c>
       <c r="I9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>30</v>
       </c>
       <c r="J9">
@@ -2684,7 +2738,7 @@
         <v>0</v>
       </c>
       <c r="K9" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -2715,7 +2769,7 @@
         <v>60</v>
       </c>
       <c r="I10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>60</v>
       </c>
       <c r="J10">
@@ -2723,7 +2777,7 @@
         <v>0</v>
       </c>
       <c r="K10" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -2754,7 +2808,7 @@
         <v>40</v>
       </c>
       <c r="I11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>40</v>
       </c>
       <c r="J11">
@@ -2762,7 +2816,7 @@
         <v>0</v>
       </c>
       <c r="K11" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -2793,7 +2847,7 @@
         <v>80</v>
       </c>
       <c r="I12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>80</v>
       </c>
       <c r="J12">
@@ -2801,7 +2855,7 @@
         <v>0</v>
       </c>
       <c r="K12" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -2832,7 +2886,7 @@
         <v>20</v>
       </c>
       <c r="I13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="J13">
@@ -2840,7 +2894,7 @@
         <v>0</v>
       </c>
       <c r="K13" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -2871,7 +2925,7 @@
         <v>90</v>
       </c>
       <c r="I14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>90</v>
       </c>
       <c r="J14">
@@ -2879,7 +2933,7 @@
         <v>0</v>
       </c>
       <c r="K14" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -2910,7 +2964,7 @@
         <v>60</v>
       </c>
       <c r="I15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>60</v>
       </c>
       <c r="J15">
@@ -2918,7 +2972,7 @@
         <v>0</v>
       </c>
       <c r="K15" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -2949,7 +3003,7 @@
         <v>120</v>
       </c>
       <c r="I16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>120</v>
       </c>
       <c r="J16">
@@ -2957,7 +3011,7 @@
         <v>0</v>
       </c>
       <c r="K16" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -2988,7 +3042,7 @@
         <v>80</v>
       </c>
       <c r="I17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>80</v>
       </c>
       <c r="J17">
@@ -2996,7 +3050,7 @@
         <v>0</v>
       </c>
       <c r="K17" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -3027,7 +3081,7 @@
         <v>100</v>
       </c>
       <c r="I18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>100</v>
       </c>
       <c r="J18">
@@ -3035,7 +3089,7 @@
         <v>0</v>
       </c>
       <c r="K18" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -3066,7 +3120,7 @@
         <v>120</v>
       </c>
       <c r="I19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>120</v>
       </c>
       <c r="J19">
@@ -3074,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="K19" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -3105,7 +3159,7 @@
         <v>120</v>
       </c>
       <c r="I20">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>120</v>
       </c>
       <c r="J20">
@@ -3113,7 +3167,7 @@
         <v>0</v>
       </c>
       <c r="K20" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -3144,7 +3198,7 @@
         <v>180</v>
       </c>
       <c r="I21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>180</v>
       </c>
       <c r="J21">
@@ -3152,7 +3206,7 @@
         <v>0</v>
       </c>
       <c r="K21" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -3183,7 +3237,7 @@
         <v>150</v>
       </c>
       <c r="I22">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>150</v>
       </c>
       <c r="J22">
@@ -3191,7 +3245,7 @@
         <v>0</v>
       </c>
       <c r="K22" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -3222,7 +3276,7 @@
         <v>240</v>
       </c>
       <c r="I23">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>240</v>
       </c>
       <c r="J23">
@@ -3230,7 +3284,7 @@
         <v>0</v>
       </c>
       <c r="K23" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -3261,7 +3315,7 @@
         <v>150</v>
       </c>
       <c r="I24">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>150</v>
       </c>
       <c r="J24">
@@ -3269,7 +3323,7 @@
         <v>0</v>
       </c>
       <c r="K24" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -3300,7 +3354,7 @@
         <v>180</v>
       </c>
       <c r="I25">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>180</v>
       </c>
       <c r="J25">
@@ -3308,7 +3362,7 @@
         <v>0</v>
       </c>
       <c r="K25" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -3339,7 +3393,7 @@
         <v>240</v>
       </c>
       <c r="I26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>240</v>
       </c>
       <c r="J26">
@@ -3347,7 +3401,7 @@
         <v>0</v>
       </c>
       <c r="K26" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -3378,7 +3432,7 @@
         <v>100</v>
       </c>
       <c r="I27">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>100</v>
       </c>
       <c r="J27">
@@ -3386,7 +3440,7 @@
         <v>0</v>
       </c>
       <c r="K27" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -3417,7 +3471,7 @@
         <v>100</v>
       </c>
       <c r="I28">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>100</v>
       </c>
       <c r="J28">
@@ -3425,7 +3479,7 @@
         <v>0</v>
       </c>
       <c r="K28" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -3456,7 +3510,7 @@
         <v>180</v>
       </c>
       <c r="I29">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>180</v>
       </c>
       <c r="J29">
@@ -3464,7 +3518,7 @@
         <v>0</v>
       </c>
       <c r="K29" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -3495,7 +3549,7 @@
         <v>90</v>
       </c>
       <c r="I30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>90</v>
       </c>
       <c r="J30">
@@ -3503,7 +3557,7 @@
         <v>0</v>
       </c>
       <c r="K30" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -3534,7 +3588,7 @@
         <v>60</v>
       </c>
       <c r="I31">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>60</v>
       </c>
       <c r="J31">
@@ -3542,7 +3596,7 @@
         <v>0</v>
       </c>
       <c r="K31" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -3573,7 +3627,7 @@
         <v>150</v>
       </c>
       <c r="I32">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>150</v>
       </c>
       <c r="J32">
@@ -3581,7 +3635,7 @@
         <v>0</v>
       </c>
       <c r="K32" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -3612,15 +3666,15 @@
         <v>120</v>
       </c>
       <c r="I33">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>120</v>
       </c>
       <c r="J33">
-        <f t="shared" ref="J33:J52" si="4">H33-I33</f>
+        <f t="shared" ref="J33:J61" si="4">H33-I33</f>
         <v>0</v>
       </c>
       <c r="K33" s="6">
-        <f t="shared" ref="K33:K52" si="5">IF(H33&gt;0, I33/H33, 0)</f>
+        <f t="shared" ref="K33:K61" si="5">IF(H33&gt;0, I33/H33, 0)</f>
         <v>1</v>
       </c>
     </row>
@@ -3651,7 +3705,7 @@
         <v>60</v>
       </c>
       <c r="I34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>60</v>
       </c>
       <c r="J34">
@@ -3690,7 +3744,7 @@
         <v>150</v>
       </c>
       <c r="I35">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>150</v>
       </c>
       <c r="J35">
@@ -3729,7 +3783,7 @@
         <v>180</v>
       </c>
       <c r="I36">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>180</v>
       </c>
       <c r="J36">
@@ -3768,7 +3822,7 @@
         <v>180</v>
       </c>
       <c r="I37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>180</v>
       </c>
       <c r="J37">
@@ -3807,7 +3861,7 @@
         <v>120</v>
       </c>
       <c r="I38">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>120</v>
       </c>
       <c r="J38">
@@ -3846,7 +3900,7 @@
         <v>45</v>
       </c>
       <c r="I39">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>45</v>
       </c>
       <c r="J39">
@@ -3885,7 +3939,7 @@
         <v>180</v>
       </c>
       <c r="I40">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>180</v>
       </c>
       <c r="J40">
@@ -3924,7 +3978,7 @@
         <v>75</v>
       </c>
       <c r="I41">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>75</v>
       </c>
       <c r="J41">
@@ -3963,7 +4017,7 @@
         <v>60</v>
       </c>
       <c r="I42">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>60</v>
       </c>
       <c r="J42">
@@ -4002,7 +4056,7 @@
         <v>120</v>
       </c>
       <c r="I43">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>120</v>
       </c>
       <c r="J43">
@@ -4041,7 +4095,7 @@
         <v>180</v>
       </c>
       <c r="I44">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>180</v>
       </c>
       <c r="J44">
@@ -4080,7 +4134,7 @@
         <v>90</v>
       </c>
       <c r="I45">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>90</v>
       </c>
       <c r="J45">
@@ -4119,7 +4173,7 @@
         <v>150</v>
       </c>
       <c r="I46">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>150</v>
       </c>
       <c r="J46">
@@ -4158,7 +4212,7 @@
         <v>240</v>
       </c>
       <c r="I47">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>240</v>
       </c>
       <c r="J47">
@@ -4197,7 +4251,7 @@
         <v>60</v>
       </c>
       <c r="I48">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>60</v>
       </c>
       <c r="J48">
@@ -4236,7 +4290,7 @@
         <v>90</v>
       </c>
       <c r="I49">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>90</v>
       </c>
       <c r="J49">
@@ -4275,7 +4329,7 @@
         <v>150</v>
       </c>
       <c r="I50">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>150</v>
       </c>
       <c r="J50">
@@ -4314,7 +4368,7 @@
         <v>60</v>
       </c>
       <c r="I51">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>60</v>
       </c>
       <c r="J51">
@@ -4353,7 +4407,7 @@
         <v>70</v>
       </c>
       <c r="I52">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>70</v>
       </c>
       <c r="J52">
@@ -4366,23 +4420,320 @@
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B53" t="s">
+        <v>124</v>
+      </c>
+      <c r="C53" t="s">
+        <v>29</v>
+      </c>
+      <c r="E53" t="s">
+        <v>125</v>
+      </c>
+      <c r="F53" t="s">
+        <v>126</v>
+      </c>
       <c r="G53" t="s">
-        <v>124</v>
+        <v>4</v>
       </c>
       <c r="H53">
-        <f>SUM(H2:H52)</f>
-        <v>5290</v>
+        <v>60</v>
       </c>
       <c r="I53">
-        <f>SUM(I2:I52)</f>
-        <v>5290</v>
+        <f>H53</f>
+        <v>60</v>
       </c>
       <c r="J53">
-        <f>SUM(J2:J52)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K53" s="6">
-        <f>I53/H53</f>
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B54" t="s">
+        <v>127</v>
+      </c>
+      <c r="C54" t="s">
+        <v>29</v>
+      </c>
+      <c r="D54" t="s">
+        <v>128</v>
+      </c>
+      <c r="E54" t="s">
+        <v>129</v>
+      </c>
+      <c r="F54" t="s">
+        <v>130</v>
+      </c>
+      <c r="G54" t="s">
+        <v>4</v>
+      </c>
+      <c r="H54">
+        <v>20</v>
+      </c>
+      <c r="I54">
+        <f>H54</f>
+        <v>20</v>
+      </c>
+      <c r="J54">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K54" s="6">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B55" t="s">
+        <v>38</v>
+      </c>
+      <c r="C55" t="s">
+        <v>131</v>
+      </c>
+      <c r="E55" t="s">
+        <v>132</v>
+      </c>
+      <c r="F55" t="s">
+        <v>133</v>
+      </c>
+      <c r="G55" t="s">
+        <v>4</v>
+      </c>
+      <c r="H55">
+        <v>20</v>
+      </c>
+      <c r="I55">
+        <f>H55</f>
+        <v>20</v>
+      </c>
+      <c r="J55">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K55" s="6">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B56" t="s">
+        <v>38</v>
+      </c>
+      <c r="C56" t="s">
+        <v>134</v>
+      </c>
+      <c r="E56" t="s">
+        <v>135</v>
+      </c>
+      <c r="F56" t="s">
+        <v>42</v>
+      </c>
+      <c r="G56" t="s">
+        <v>4</v>
+      </c>
+      <c r="H56">
+        <v>20</v>
+      </c>
+      <c r="I56">
+        <f>H56</f>
+        <v>20</v>
+      </c>
+      <c r="J56">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K56" s="6">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B57" t="s">
+        <v>38</v>
+      </c>
+      <c r="C57" t="s">
+        <v>134</v>
+      </c>
+      <c r="D57" t="s">
+        <v>136</v>
+      </c>
+      <c r="E57" t="s">
+        <v>137</v>
+      </c>
+      <c r="F57" t="s">
+        <v>138</v>
+      </c>
+      <c r="G57" t="s">
+        <v>4</v>
+      </c>
+      <c r="H57">
+        <v>80</v>
+      </c>
+      <c r="I57">
+        <f>H57</f>
+        <v>80</v>
+      </c>
+      <c r="J57">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K57" s="6">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B58" t="s">
+        <v>38</v>
+      </c>
+      <c r="C58" t="s">
+        <v>134</v>
+      </c>
+      <c r="D58" t="s">
+        <v>136</v>
+      </c>
+      <c r="E58" t="s">
+        <v>139</v>
+      </c>
+      <c r="F58" t="s">
+        <v>126</v>
+      </c>
+      <c r="G58" t="s">
+        <v>4</v>
+      </c>
+      <c r="H58">
+        <v>15</v>
+      </c>
+      <c r="I58">
+        <f>H58</f>
+        <v>15</v>
+      </c>
+      <c r="J58">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K58" s="6">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B59" t="s">
+        <v>38</v>
+      </c>
+      <c r="C59" t="s">
+        <v>72</v>
+      </c>
+      <c r="E59" t="s">
+        <v>140</v>
+      </c>
+      <c r="F59" t="s">
+        <v>42</v>
+      </c>
+      <c r="G59" t="s">
+        <v>4</v>
+      </c>
+      <c r="H59">
+        <v>20</v>
+      </c>
+      <c r="I59">
+        <f>H59</f>
+        <v>20</v>
+      </c>
+      <c r="J59">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K59" s="6">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B60" t="s">
+        <v>38</v>
+      </c>
+      <c r="C60" t="s">
+        <v>72</v>
+      </c>
+      <c r="D60" t="s">
+        <v>136</v>
+      </c>
+      <c r="E60" t="s">
+        <v>141</v>
+      </c>
+      <c r="F60" t="s">
+        <v>126</v>
+      </c>
+      <c r="G60" t="s">
+        <v>4</v>
+      </c>
+      <c r="H60">
+        <v>120</v>
+      </c>
+      <c r="I60">
+        <f>H60</f>
+        <v>120</v>
+      </c>
+      <c r="J60">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K60" s="6">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B61" t="s">
+        <v>38</v>
+      </c>
+      <c r="C61" t="s">
+        <v>72</v>
+      </c>
+      <c r="E61" t="s">
+        <v>142</v>
+      </c>
+      <c r="F61" t="s">
+        <v>126</v>
+      </c>
+      <c r="G61" t="s">
+        <v>4</v>
+      </c>
+      <c r="H61">
+        <v>30</v>
+      </c>
+      <c r="I61">
+        <f>H61</f>
+        <v>30</v>
+      </c>
+      <c r="J61">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K61" s="6">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="H62">
+        <f>SUM(H2:H61)</f>
+        <v>5675</v>
+      </c>
+      <c r="I62">
+        <f t="shared" ref="I62:J62" si="6">SUM(I2:I61)</f>
+        <v>5675</v>
+      </c>
+      <c r="J62">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="K62" s="6">
+        <f>I61/H61</f>
         <v>1</v>
       </c>
     </row>
